--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128539493</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128539493</v>
       </c>
       <c r="B3" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128539493</v>
       </c>
       <c r="B3" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128539493</v>
       </c>
       <c r="B3" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128537785</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128537785</v>
+        <v>128539493</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583977</v>
+        <v>583905</v>
       </c>
       <c r="R2" t="n">
-        <v>6574703</v>
+        <v>6574606</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128539493</v>
+        <v>128539329</v>
       </c>
       <c r="B3" t="n">
-        <v>58093</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,11 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583905</v>
+        <v>584004</v>
       </c>
       <c r="R3" t="n">
-        <v>6574606</v>
+        <v>6574600</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +911,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128537785</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svedtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>583977</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6574703</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40857-2025 artfynd.xlsx
+++ b/artfynd/A 40857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,8 +1045,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128537785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>